--- a/human_resources_forms/017_emergency_contact_information_form--human_resources_forms.xlsx
+++ b/human_resources_forms/017_emergency_contact_information_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,19 +520,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>emergency_contact_name</t>
+          <t>emergency_contact_info_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Emergency Contact Name</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Enter participant's name</t>
-        </is>
-      </c>
+          <t>Participant's Emergency Contact 1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -547,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>relationship</t>
+          <t>participant_relationship_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Relationship to Participant 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -570,22 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>contact_phone_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Contact Phone</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Enter phone number</t>
-        </is>
-      </c>
+          <t>Emergency Contact 1 Phone</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -597,19 +589,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>contact_email_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Contact Email</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Enter participant's email</t>
-        </is>
-      </c>
+          <t>Emergency Contact 1 Email</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -624,22 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>contact_address</t>
+          <t>contact_address_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Contact Address</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Enter participant's address</t>
-        </is>
-      </c>
+          <t>Emergency Contact 1 Address</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -651,19 +635,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>emergency_contact_name_2</t>
+          <t>emergency_contact_info_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Emergency Contact Name</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Enter emergency contact's name</t>
-        </is>
-      </c>
+          <t>Another Emergency Contact</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -678,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>relationship_2</t>
+          <t>participant_relationship_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Relationship to Participant 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -706,14 +686,10 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Contact Phone</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Enter emergency contact's phone number</t>
-        </is>
-      </c>
+          <t>Emergency Contact 2 Phone</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -733,14 +709,10 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Contact Email</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Enter emergency contact's email</t>
-        </is>
-      </c>
+          <t>Emergency Contact 2 Email</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -760,14 +732,10 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Contact Address</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Enter emergency contact's address</t>
-        </is>
-      </c>
+          <t>Emergency Contact 2 Address</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -788,7 +756,7 @@
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
@@ -813,7 +781,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>relationship_choices</t>
+          <t>participant_relationship_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -830,7 +798,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>relationship_choices</t>
+          <t>participant_relationship_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -847,7 +815,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>relationship_choices</t>
+          <t>participant_relationship_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -864,7 +832,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>relationship_choices</t>
+          <t>participant_relationship_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -881,7 +849,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>relationship_choices</t>
+          <t>participant_relationship_1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -898,7 +866,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>relationship_choices</t>
+          <t>participant_relationship_1_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -915,7 +883,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>relationship_choices</t>
+          <t>participant_relationship_1_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -932,7 +900,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>relationship_choices</t>
+          <t>participant_relationship_1_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -949,7 +917,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>relationship_2_choices</t>
+          <t>participant_relationship_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -966,7 +934,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>relationship_2_choices</t>
+          <t>participant_relationship_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -983,7 +951,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>relationship_2_choices</t>
+          <t>participant_relationship_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1000,7 +968,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>relationship_2_choices</t>
+          <t>participant_relationship_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1017,7 +985,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>relationship_2_choices</t>
+          <t>participant_relationship_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1034,7 +1002,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>relationship_2_choices</t>
+          <t>participant_relationship_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1051,7 +1019,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>relationship_2_choices</t>
+          <t>participant_relationship_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1068,7 +1036,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>relationship_2_choices</t>
+          <t>participant_relationship_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
